--- a/test/fixtures/files/success.xlsx
+++ b/test/fixtures/files/success.xlsx
@@ -329,7 +329,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="56.1" min="1" max="1" bestFit="1" customWidth="1"/>
@@ -340,7 +340,7 @@
     <col width="16.5" min="6" max="6" bestFit="1" customWidth="1"/>
     <col width="26.400000000000002" min="7" max="7" bestFit="1" customWidth="1"/>
     <col width="20.900000000000002" min="8" max="8" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="9" max="9" bestFit="1" customWidth="1"/>
+    <col width="26.400000000000002" min="9" max="9" bestFit="1" customWidth="1"/>
     <col width="12.100000000000001" min="10" max="10" bestFit="1" customWidth="1"/>
     <col width="22.0" min="11" max="11" bestFit="1" customWidth="1"/>
     <col width="9.9" min="12" max="12" bestFit="1" customWidth="1"/>
@@ -489,16 +489,20 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="n">
-        <v>102</v>
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
           <t>Orin Thistle</t>
         </is>
       </c>
-      <c r="C5" s="0" t="n">
-        <v>2</v>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>0000000000002</t>
+        </is>
       </c>
       <c r="D5" s="0"/>
       <c r="E5" s="0" t="n">
@@ -522,16 +526,20 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="n">
-        <v>103</v>
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
           <t>Vela Reed</t>
         </is>
       </c>
-      <c r="C6" s="0" t="n">
-        <v>3</v>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>0000000000003</t>
+        </is>
       </c>
       <c r="D6" s="0"/>
       <c r="E6" s="0" t="inlineStr">
@@ -553,8 +561,10 @@
           <t>Elo Moss</t>
         </is>
       </c>
-      <c r="C7" s="0" t="n">
-        <v>4</v>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>0000000000004</t>
+        </is>
       </c>
       <c r="D7" s="0"/>
       <c r="E7" s="0" t="inlineStr">
@@ -586,6 +596,21 @@
       <c r="L8" s="0"/>
       <c r="M8" s="0"/>
       <c r="N8" s="0"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="0"/>
+      <c r="B9" s="0"/>
+      <c r="C9" s="0"/>
+      <c r="D9" s="0"/>
+      <c r="E9" s="0"/>
+      <c r="F9" s="0"/>
+      <c r="G9" s="0"/>
+      <c r="H9" s="0"/>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>Fictional timing note</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetCalcPr fullCalcOnLoad="1"/>
